--- a/artfynd/A 29448-2023 artfynd.xlsx
+++ b/artfynd/A 29448-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29448-2023 artfynd.xlsx
+++ b/artfynd/A 29448-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102305892</v>
+        <v>102341273</v>
       </c>
       <c r="B2" t="n">
-        <v>44328</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>201164</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnhult 24, Habo, Vg</t>
+          <t>Brandstorp strand , Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452738.5052660414</v>
+        <v>452842</v>
       </c>
       <c r="R2" t="n">
-        <v>6436655.006960177</v>
+        <v>6436527</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,22 +742,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,52 +784,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102341273</v>
+        <v>102305892</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>201164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brandstorp strand , Vg</t>
+          <t>Björnhult 24, Habo, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452842.4674034807</v>
+        <v>452739</v>
       </c>
       <c r="R3" t="n">
-        <v>6436527.336365039</v>
+        <v>6436655</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,6 +885,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5063386</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>JUNGFRUBERGET (07E7b02), Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>452790</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6436585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1995-10-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1995-10-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>070471021 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:2,3 ha</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Kindbom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29448-2023 artfynd.xlsx
+++ b/artfynd/A 29448-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102341273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102305892</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,8 +1006,18 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5063386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>